--- a/AtchisonRegime/Outputs/China/df_regInflation_China.xlsx
+++ b/AtchisonRegime/Outputs/China/df_regInflation_China.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11479,24 +11479,50 @@
         <v>45747</v>
       </c>
       <c r="B425" t="n">
-        <v>-0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="C425" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0.7138888888888889</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1.038722505987304</v>
+      </c>
+      <c r="F425" t="b">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>-0.7835479487520001</v>
+      </c>
+      <c r="H425" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B426" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C426" t="n">
         <v>-0.3</v>
       </c>
-      <c r="D425" t="n">
-        <v>0.6972222222222223</v>
-      </c>
-      <c r="E425" t="n">
-        <v>1.056810865930752</v>
-      </c>
-      <c r="F425" t="b">
-        <v>0</v>
-      </c>
-      <c r="G425" t="n">
-        <v>-0.9436146564825021</v>
-      </c>
-      <c r="H425" t="b">
+      <c r="D426" t="n">
+        <v>0.6527777777777779</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1.019379674427061</v>
+      </c>
+      <c r="F426" t="b">
+        <v>0</v>
+      </c>
+      <c r="G426" t="n">
+        <v>-0.9346642881743581</v>
+      </c>
+      <c r="H426" t="b">
         <v>0</v>
       </c>
     </row>
